--- a/XBRL-template-MPERS/Group/13-Notes-ListOfNotes.xlsx
+++ b/XBRL-template-MPERS/Group/13-Notes-ListOfNotes.xlsx
@@ -466,588 +466,588 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure of notes and other explanatory information [abstract]</t>
+          <t>Disclosure of notes and other explanatory information</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Disclosure of acquisition and disposal of subsidiary [text block]</t>
+          <t>Disclosure of acquisition and disposal of subsidiary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Disclosure of auditors' remuneration [text block]</t>
+          <t>Disclosure of auditors' remuneration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Disclosure of authorisation of financial statements [text block]</t>
+          <t>Disclosure of authorisation of financial statements</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Disclosure of basis of preparation of financial statements [text block]</t>
+          <t>Disclosure of basis of preparation of financial statements</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Disclosure of biological assets [text block]</t>
+          <t>Disclosure of biological assets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Disclosure of borrowings [text block]</t>
+          <t>Disclosure of borrowings</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Disclosure of capital and reserves [text block]</t>
+          <t>Disclosure of capital and reserves</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Disclosure of cash and cash equivalents [text block]</t>
+          <t>Disclosure of cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Disclosure of changes in accounting policies, accounting estimates and errors [text block]</t>
+          <t>Disclosure of changes in accounting policies, accounting estimates and errors</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Disclosure of claims and benefits paid [text block]</t>
+          <t>Disclosure of claims and benefits paid</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Disclosure of collateral [text block]</t>
+          <t>Disclosure of collateral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Disclosure of commitments [text block]</t>
+          <t>Disclosure of commitments</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Disclosure of contingent assets and contingent liabilities [text block]</t>
+          <t>Disclosure of contingent assets and contingent liabilities</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Disclosure of convertible notes [text block]</t>
+          <t>Disclosure of convertible notes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Disclosure of cost of sales [text block]</t>
+          <t>Disclosure of cost of sales</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Disclosure of credit risk [text block]</t>
+          <t>Disclosure of credit risk</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Disclosure of current tax assets or current tax liabilities [text block]</t>
+          <t>Disclosure of current tax assets or current tax liabilities</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Disclosure of deferred income [text block]</t>
+          <t>Disclosure of deferred income</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Disclosure of deferred tax assets/(liabilities) [text block]</t>
+          <t>Disclosure of deferred tax assets/(liabilities)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Disclosure of deposits from banks [text block]</t>
+          <t>Disclosure of deposits from banks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Disclosure of depreciation and amortisation expense [text block]</t>
+          <t>Disclosure of depreciation and amortisation expense</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Disclosure of derivative financial instruments [text block]</t>
+          <t>Disclosure of derivative financial instruments</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Disclosure of discontinued operations [text block]</t>
+          <t>Disclosure of discontinued operations</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Disclosure of dividends [text block]</t>
+          <t>Disclosure of dividends</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Disclosure of earnings/loss per share [text block]</t>
+          <t>Disclosure of earnings/loss per share</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Disclosure of effect of changes in foreign exchange rates [text block]</t>
+          <t>Disclosure of effect of changes in foreign exchange rates</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Disclosure of employment termination benefits [text block]</t>
+          <t>Disclosure of employment termination benefits</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Disclosure of entity's operating segments [text block]</t>
+          <t>Disclosure of entity's operating segments</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Disclosure of explanation of transition to the MPERS [text block]</t>
+          <t>Disclosure of explanation of transition to the MPERS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Disclosure of fee and commission income (expense) [text block]</t>
+          <t>Disclosure of fee and commission income (expense)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Disclosure of finance costs [text block]</t>
+          <t>Disclosure of finance costs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Disclosure of finance income [text block]</t>
+          <t>Disclosure of finance income</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Disclosure of financial instruments [text block]</t>
+          <t>Disclosure of financial instruments</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Disclosure of financial instrument measured at amortised cost [text block]</t>
+          <t>Disclosure of financial instrument measured at amortised cost</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Disclosure of financial instruments at fair value through profit or loss [text block]</t>
+          <t>Disclosure of financial instruments at fair value through profit or loss</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Disclosure of first-time adoption [text block]</t>
+          <t>Disclosure of first-time adoption</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Disclosure of foreign currency [text block]</t>
+          <t>Disclosure of foreign currency</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Disclosure of general information about financial statements [text block]</t>
+          <t>Disclosure of general information about financial statements</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Disclosure of going concern [text block]</t>
+          <t>Disclosure of going concern</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Disclosure of government grants [text block]</t>
+          <t>Disclosure of government grants</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Disclosure of hedging activities [text block]</t>
+          <t>Disclosure of hedging activities</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Disclosure of impairment of assets [text block]</t>
+          <t>Disclosure of impairment of assets</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Disclosure of income tax expense [text block]</t>
+          <t>Disclosure of income tax expense</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Disclosure of intangible assets [text block]</t>
+          <t>Disclosure of intangible assets</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Disclosure of interest expense [text block]</t>
+          <t>Disclosure of interest expense</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Disclosure of interest in associates, joint ventures or jointly controlled operation [text block]</t>
+          <t>Disclosure of interest in associates, joint ventures or jointly controlled operation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Disclosure of interest income [text block]</t>
+          <t>Disclosure of interest income</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Disclosure of inventories [text block]</t>
+          <t>Disclosure of inventories</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Disclosure of investment in jointly controlled entities [text block]</t>
+          <t>Disclosure of investment in jointly controlled entities</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Disclosure of investment in subsidiaries [text block]</t>
+          <t>Disclosure of investment in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Disclosure of investment property [text block]</t>
+          <t>Disclosure of investment property</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Disclosure of investment in associates [text block]</t>
+          <t>Disclosure of investment in associates</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Disclosure of leases [text block]</t>
+          <t>Disclosure of leases</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Disclosure of liquidity risk [text block]</t>
+          <t>Disclosure of liquidity risk</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Disclosure of loans and advances to banks [text block]</t>
+          <t>Disclosure of loans and advances to banks</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Disclosure of market risk [text block]</t>
+          <t>Disclosure of market risk</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Disclosure of non-adjusting events after the end of reporting period [text block]</t>
+          <t>Disclosure of non-adjusting events after the end of reporting period</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Disclosure of non-controlling interests [text block]</t>
+          <t>Disclosure of non-controlling interests</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Disclosure of non-current assets or disposal groups classified as held for sale [text block]</t>
+          <t>Disclosure of non-current assets or disposal groups classified as held for sale</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Disclosure of other comprehensive income [text block]</t>
+          <t>Disclosure of other comprehensive income</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Disclosure of other current assets [text block]</t>
+          <t>Disclosure of other current assets</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Disclosure of other current liabilities [text block]</t>
+          <t>Disclosure of other current liabilities</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Disclosure of other income [text block]</t>
+          <t>Disclosure of other income</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Disclosure of other investments [text block]</t>
+          <t>Disclosure of other investments</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Disclosure of other long-term employment benefits [text block]</t>
+          <t>Disclosure of other long-term employment benefits</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Disclosure of other non-current assets [text block]</t>
+          <t>Disclosure of other non-current assets</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Disclosure of other non-current liabilities [text block]</t>
+          <t>Disclosure of other non-current liabilities</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Disclosure of other notes to accounts [text block]</t>
+          <t>Disclosure of other notes to accounts</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Disclosure of other operating expense [text block]</t>
+          <t>Disclosure of other operating expense</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Disclosure of other reserves [text block]</t>
+          <t>Disclosure of other reserves</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Disclosure of perpetual sukuk [text block]</t>
+          <t>Disclosure of perpetual sukuk</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Disclosure of post employment benefit obligation [text block]</t>
+          <t>Disclosure of post employment benefit obligation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Disclosure of profit or loss for the year [text block]</t>
+          <t>Disclosure of profit or loss for the year</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Disclosure of property, plant and equipment [text block]</t>
+          <t>Disclosure of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Disclosure of provisions [text block]</t>
+          <t>Disclosure of provisions</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Disclosure of redeemable preference shares [text block]</t>
+          <t>Disclosure of redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Disclosure of revenue [text block]</t>
+          <t>Disclosure of revenue</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Disclosure of service concession arrangements [text block]</t>
+          <t>Disclosure of service concession arrangements</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Disclosure of share capital [text block]</t>
+          <t>Disclosure of share capital</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Disclosure of share-based payment arrangements [text block]</t>
+          <t>Disclosure of share-based payment arrangements</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Disclosure of subsequent event [text block]</t>
+          <t>Disclosure of subsequent event</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Disclosure of trade and other payables [text block]</t>
+          <t>Disclosure of trade and other payables</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Disclosure of trade and other receivables [text block]</t>
+          <t>Disclosure of trade and other receivables</t>
         </is>
       </c>
     </row>

--- a/XBRL-template-MPERS/Group/13-Notes-ListOfNotes.xlsx
+++ b/XBRL-template-MPERS/Group/13-Notes-ListOfNotes.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +475,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure of notes and other explanatory information</t>
         </is>
